--- a/literature-review/snowballing/snowballing_topic3.xlsx
+++ b/literature-review/snowballing/snowballing_topic3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FBFFD2-D400-4032-8B2F-B429B20A52DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328C2F5D-6F32-4F4C-8155-B7D0AF8755CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8784" yWindow="1200" windowWidth="26556" windowHeight="14496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6696" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
   <si>
     <t>Backward Snowballing Results</t>
   </si>
@@ -118,18 +118,6 @@
   </si>
   <si>
     <t>https://openaccess.thecvf.com/content/CVPR2021W/EarthVision/html/Verma_QFabric_Multi-Task_Change_Detection_Dataset_CVPRW_2021_paper.html</t>
-  </si>
-  <si>
-    <t>Assessing machine learning based supervised classifiers for built-up impervious surface area extraction from sentinel-2 images</t>
-  </si>
-  <si>
-    <t>M Misra, D Kumar, S Shekhar - Urban Forestry &amp; Urban Greening</t>
-  </si>
-  <si>
-    <t>Urban Forestry &amp; Urban Greening</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S1618866720302326</t>
   </si>
   <si>
     <t>Urban impervious surface detection from remote sensing images: A review of the methods and challenges</t>
@@ -224,7 +212,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFC4D79B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -325,6 +313,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -338,15 +327,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC4D79B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -621,22 +612,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.89453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="60.77734375" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" customWidth="1"/>
-    <col min="4" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="16" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.7890625" customWidth="1"/>
+    <col min="2" max="2" width="60.7890625" customWidth="1"/>
+    <col min="3" max="3" width="30.7890625" customWidth="1"/>
+    <col min="4" max="8" width="10.7890625" customWidth="1"/>
+    <col min="9" max="16" width="8.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" ht="23.1" x14ac:dyDescent="0.85">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="I2" s="2" t="s">
         <v>1</v>
       </c>
@@ -647,7 +638,7 @@
       </c>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -699,359 +690,371 @@
       <c r="Q3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="19"/>
-    </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="11">
         <v>0</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="12">
         <v>2020</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="12">
         <v>254</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="K4" s="14" t="s">
+      <c r="I4" s="14"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="15"/>
-      <c r="Q4" s="13"/>
-    </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+      <c r="L4" s="16"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="12">
         <v>2021</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="12">
         <v>28</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="K5" s="14" t="s">
+      <c r="I5" s="17"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="17"/>
-      <c r="Q5" s="16"/>
-    </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="12"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E6" s="11">
-        <v>44</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="D6" s="12">
+        <v>2019</v>
+      </c>
+      <c r="E6" s="12">
+        <v>75</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="K6" s="14" t="s">
+      <c r="I6" s="17"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="17"/>
-      <c r="Q6" s="16"/>
-    </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E7" s="11">
-        <v>75</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="16"/>
-      <c r="K7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="17"/>
-      <c r="Q7" s="16"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="8"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="8"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="H10" s="7"/>
-    </row>
-    <row r="12" spans="1:18" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B12" s="1" t="s">
+    <row r="11" spans="1:18" ht="23.1" x14ac:dyDescent="0.85">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="I13" s="2" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="I12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="2" t="s">
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="5" t="s">
+      <c r="L13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="Q13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="R14" s="19"/>
-    </row>
-    <row r="15" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
+      <c r="R13" s="10"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="12">
         <v>0</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B14" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="12">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="16"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="12">
+        <v>1</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="12">
+        <v>2024</v>
+      </c>
+      <c r="E15" s="12">
+        <v>17</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="R15" s="12"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="12">
+        <v>2</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="12">
         <v>2024</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E16" s="12">
         <v>0</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="12"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="12">
+        <v>3</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12">
+        <v>2024</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="K15" s="14" t="s">
+      <c r="H17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="17"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="15"/>
-      <c r="Q15" s="13"/>
-    </row>
-    <row r="16" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
-        <v>1</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="11">
-        <v>2024</v>
-      </c>
-      <c r="E16" s="11">
-        <v>17</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="16"/>
-      <c r="K16" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="17"/>
-      <c r="Q16" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
-        <v>2</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="11">
-        <v>2024</v>
-      </c>
-      <c r="E17" s="11">
-        <v>0</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="K17" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="17"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
-        <v>3</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="11">
-        <v>2024</v>
-      </c>
-      <c r="E18" s="11">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" s="16"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="17"/>
-      <c r="Q18" s="16"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="12"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="H23" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
